--- a/Ejercicio Sencillo de IRRBB.xlsx
+++ b/Ejercicio Sencillo de IRRBB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\OneDrive\Desktop\TRABAJO\UNI\8VO SEMESTRE\ADMINISTRACION_RIESGOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC8872D-030A-4D82-A56C-B9594D336575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80BF464F-B7A5-4228-95D2-9F532DB51A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{18416E51-0E84-41AD-A4BD-93EEE06D55BC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{18416E51-0E84-41AD-A4BD-93EEE06D55BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -835,22 +835,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{702C9248-0FF7-4BED-A5D3-5C97C39BEEF6}">
   <dimension ref="B1:O47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
@@ -863,7 +863,7 @@
       <c r="G4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>0</v>
       </c>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>2</v>
       </c>
@@ -891,7 +891,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
         <v>1</v>
       </c>
@@ -905,7 +905,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
         <v>3</v>
       </c>
@@ -917,7 +917,7 @@
       <c r="G8" s="4"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>8</v>
       </c>
@@ -931,7 +931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="12" t="s">
         <v>9</v>
       </c>
@@ -945,7 +945,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>10</v>
       </c>
@@ -959,7 +959,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="4" t="s">
         <v>11</v>
       </c>
@@ -970,15 +970,15 @@
       <c r="G13" s="4"/>
       <c r="I13" s="4"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" s="6"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
         <v>16</v>
       </c>
@@ -986,7 +986,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" s="6"/>
       <c r="C20">
         <f>C7*0.02</f>
@@ -996,10 +996,10 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" s="6"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B22" s="7" t="s">
         <v>17</v>
       </c>
@@ -1007,7 +1007,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B23" s="6"/>
       <c r="C23">
         <f>C10*0.01+C11*0.02</f>
@@ -1017,10 +1017,10 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24" s="6"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
         <v>18</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>30</v>
       </c>
@@ -1040,23 +1040,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B31" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" s="8"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="9"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="11" t="s">
         <v>21</v>
       </c>
@@ -1068,15 +1068,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="6"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>23</v>
       </c>
@@ -1085,10 +1085,10 @@
         <v>-0.26</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="8"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="10" t="s">
         <v>24</v>
       </c>
@@ -1096,25 +1096,25 @@
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="8"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
         <v>37</v>
       </c>
